--- a/data/trans_orig/P57B3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido solo/a en 2023</t>
+          <t>Población según se ha sentido solo/a en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>90561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132322</t>
+          <t>132721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107832</t>
+          <t>108250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>181634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230275</t>
+          <t>232095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175283</t>
+          <t>175823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217852</t>
+          <t>217412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176809</t>
+          <t>176926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202257</t>
+          <t>202472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>363079</t>
+          <t>361037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>411757</t>
+          <t>410369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,47 +1349,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>20721</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>12836</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>34360</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>20721</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>13115</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>33645</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47356</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51558</t>
+          <t>51888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55015</t>
+          <t>55794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87174</t>
+          <t>89151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164716</t>
+          <t>165697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>225164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160864</t>
+          <t>159914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>198833</t>
+          <t>199753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335466</t>
+          <t>336280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410935</t>
+          <t>409426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>253575</t>
+          <t>253664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313659</t>
+          <t>313819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>263836</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>301373</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>530609</t>
+          <t>531137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>608074</t>
+          <t>604754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22451</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39147</t>
+          <t>38813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61593</t>
+          <t>61636</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56654</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52098</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76590</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93278</t>
+          <t>92952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124554</t>
+          <t>125208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222702</t>
+          <t>223398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>250686</t>
+          <t>252130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223669</t>
+          <t>224027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252630</t>
+          <t>252676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454192</t>
+          <t>455883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>495508</t>
+          <t>496038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>50765</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97154</t>
+          <t>98074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94607</t>
+          <t>94580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160659</t>
+          <t>156306</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220865</t>
+          <t>219486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257147</t>
+          <t>255649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>338191</t>
+          <t>336843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>410673</t>
+          <t>408993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>571461</t>
+          <t>574283</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>656212</t>
+          <t>657046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>74018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96472</t>
+          <t>96755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97308</t>
+          <t>97199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>117290</t>
+          <t>117222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>178421</t>
+          <t>177169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208142</t>
+          <t>206769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57590</t>
+          <t>56656</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>79911</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67121</t>
+          <t>68040</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>130619</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>160116</t>
+          <t>162033</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38892</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>30788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55829</t>
+          <t>55998</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>43965</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53359</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77133</t>
+          <t>77514</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>181226</t>
+          <t>183167</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>207564</t>
+          <t>207512</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>180818</t>
+          <t>180210</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>201010</t>
+          <t>200225</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>371024</t>
+          <t>371505</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>402724</t>
+          <t>403390</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>37836</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>62353</t>
+          <t>63013</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40850</t>
+          <t>40878</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>52829</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84428</t>
+          <t>83173</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>148918</t>
+          <t>150825</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>204703</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>90416</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>275904</t>
+          <t>277140</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>241346</t>
+          <t>233011</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>452018</t>
+          <t>451912</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>370290</t>
+          <t>370766</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>428837</t>
+          <t>427540</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>489490</t>
+          <t>488887</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>738803</t>
+          <t>721841</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>890715</t>
+          <t>890653</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1170270</t>
+          <t>1162956</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>59121</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>641866</t>
+          <t>629485</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>46751</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>69506</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>117178</t>
+          <t>115772</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>840945</t>
+          <t>835017</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>52708</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>153248</t>
+          <t>152275</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>113230</t>
+          <t>112671</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>147464</t>
+          <t>148541</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>139229</t>
+          <t>141220</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>286415</t>
+          <t>286722</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>152116</t>
+          <t>162639</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>471437</t>
+          <t>471583</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>352931</t>
+          <t>355232</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>401960</t>
+          <t>402887</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>452722</t>
+          <t>453879</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>854595</t>
+          <t>858192</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>84543</t>
+          <t>88267</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>267058</t>
+          <t>270088</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>134125</t>
+          <t>133552</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>173946</t>
+          <t>174824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>206260</t>
+          <t>212282</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>410887</t>
+          <t>414863</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>127244</t>
+          <t>126748</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1040145</t>
+          <t>1119406</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>114171</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>160826</t>
+          <t>159945</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>261836</t>
+          <t>263767</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1454463</t>
+          <t>1372465</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>184248</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>275812</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>249101</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>334553</t>
+          <t>337159</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>469975</t>
+          <t>470160</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>595762</t>
+          <t>592055</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>823630</t>
+          <t>818316</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1137197</t>
+          <t>1133051</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>933543</t>
+          <t>939586</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1224976</t>
+          <t>1225748</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1884033</t>
+          <t>1867144</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2313594</t>
+          <t>2325161</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1401663</t>
+          <t>1350780</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1976983</t>
+          <t>1979854</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1958955</t>
+          <t>1959813</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2380505</t>
+          <t>2344653</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3463186</t>
+          <t>3482742</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4153567</t>
+          <t>4132562</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Provincia-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109794</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90561</t>
+          <t>91151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132721</t>
+          <t>127186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95297</t>
+          <t>102753</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>89846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108250</t>
+          <t>116448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>205091</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181634</t>
+          <t>191557</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232095</t>
+          <t>234499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>197905</t>
+          <t>206234</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175823</t>
+          <t>188632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217412</t>
+          <t>223703</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>189714</t>
+          <t>208295</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176926</t>
+          <t>194799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>220692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>387619</t>
+          <t>414529</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361037</t>
+          <t>391324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410369</t>
+          <t>435026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,22 +1329,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20721</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34360</t>
+          <t>34841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>43006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31222</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51888</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>70861</t>
+          <t>74780</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55794</t>
+          <t>59724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89151</t>
+          <t>93388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>192670</t>
+          <t>197216</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165697</t>
+          <t>169000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225164</t>
+          <t>224599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>178988</t>
+          <t>192134</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159914</t>
+          <t>172679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199753</t>
+          <t>214130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>371657</t>
+          <t>389350</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>336280</t>
+          <t>353911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409426</t>
+          <t>424481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>285120</t>
+          <t>291619</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>253664</t>
+          <t>261747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313819</t>
+          <t>317664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>283040</t>
+          <t>297790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>263836</t>
+          <t>275571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>317725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>568160</t>
+          <t>589409</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>531137</t>
+          <t>553498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>604754</t>
+          <t>623518</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31222</t>
+          <t>34506</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41432</t>
+          <t>45468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38813</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61636</t>
+          <t>63807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44127</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34007</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63658</t>
+          <t>62789</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>52514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107785</t>
+          <t>108135</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92952</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125208</t>
+          <t>125303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>238290</t>
+          <t>235227</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223398</t>
+          <t>219524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>248994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>238447</t>
+          <t>242568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224027</t>
+          <t>228003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252676</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>476738</t>
+          <t>477796</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>455883</t>
+          <t>456629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>496038</t>
+          <t>495226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>39433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>73197</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41537</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75444</t>
+          <t>95146</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>83819</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>69980</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>131220</t>
+          <t>157016</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>133839</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>156306</t>
+          <t>182576</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>239349</t>
+          <t>281299</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219486</t>
+          <t>258616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255649</t>
+          <t>301749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>367290</t>
+          <t>300266</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>336843</t>
+          <t>283586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408993</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>606639</t>
+          <t>581566</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>574283</t>
+          <t>552824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>657046</t>
+          <t>608211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,22 +3071,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>31946</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>49730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>84987</t>
+          <t>99018</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74018</t>
+          <t>86401</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>111655</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>107093</t>
+          <t>115485</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97199</t>
+          <t>105360</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>117222</t>
+          <t>127407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>192080</t>
+          <t>214502</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177169</t>
+          <t>197609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206769</t>
+          <t>231048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68115</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>63112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>79630</t>
+          <t>87485</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>77605</t>
+          <t>84725</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>73996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87106</t>
+          <t>95415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>145720</t>
+          <t>160330</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>130619</t>
+          <t>144296</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>162033</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,67 +3605,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>33528</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>26542</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>42758</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>29968</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>23665</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>39118</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>46748</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55998</t>
+          <t>57954</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43965</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>32348</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>64206</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>53604</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77514</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>195716</t>
+          <t>194415</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>183167</t>
+          <t>181161</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>207512</t>
+          <t>206082</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>191344</t>
+          <t>194702</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>180210</t>
+          <t>182228</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>200225</t>
+          <t>203550</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>387060</t>
+          <t>389117</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>371505</t>
+          <t>372782</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>403390</t>
+          <t>404273</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37836</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>56714</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>71055</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>27646</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>51537</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>57934</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>63597</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>61967</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>97392</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>174683</t>
+          <t>194213</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>150825</t>
+          <t>166277</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>221730</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>201817</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>90416</t>
+          <t>212016</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>277140</t>
+          <t>257112</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>376500</t>
+          <t>430767</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>233011</t>
+          <t>394904</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>451912</t>
+          <t>465551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>399767</t>
+          <t>464087</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>370766</t>
+          <t>432791</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>427540</t>
+          <t>492222</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>583630</t>
+          <t>458273</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>488887</t>
+          <t>434723</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>721841</t>
+          <t>483009</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>983397</t>
+          <t>922360</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>890653</t>
+          <t>886992</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1162956</t>
+          <t>960297</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>291941</t>
+          <t>61645</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>629485</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,67 +4743,67 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>129012</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>111924</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>151983</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>348796</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>115772</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>835017</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>106434</t>
+          <t>120274</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>52708</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>152275</t>
+          <t>142061</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>129633</t>
+          <t>152213</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>112671</t>
+          <t>134064</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>148541</t>
+          <t>174131</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>236067</t>
+          <t>272488</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>141220</t>
+          <t>246371</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>286722</t>
+          <t>301373</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>339634</t>
+          <t>394258</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>162639</t>
+          <t>364088</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>471583</t>
+          <t>423823</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>378185</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>355232</t>
+          <t>401856</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>402887</t>
+          <t>453639</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>717819</t>
+          <t>822173</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>453879</t>
+          <t>786005</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>858192</t>
+          <t>868539</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>189685</t>
+          <t>220741</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>88267</t>
+          <t>189704</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>270088</t>
+          <t>248328</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>153059</t>
+          <t>183836</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>133552</t>
+          <t>161870</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>174824</t>
+          <t>207725</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>342744</t>
+          <t>404576</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>212282</t>
+          <t>366876</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>414863</t>
+          <t>438037</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>370173</t>
+          <t>148181</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>126748</t>
+          <t>126418</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1119406</t>
+          <t>173837</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>138186</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>112890</t>
+          <t>141049</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>182927</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>508360</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>263767</t>
+          <t>277260</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1372465</t>
+          <t>342071</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>239160</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>239458</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>273593</t>
+          <t>309049</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>344256</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>245828</t>
+          <t>316348</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>378300</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>541464</t>
+          <t>613115</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>470160</t>
+          <t>570572</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>592055</t>
+          <t>658392</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1034644</t>
+          <t>1144414</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>818316</t>
+          <t>1084585</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1133051</t>
+          <t>1212257</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1131713</t>
+          <t>1253798</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>939586</t>
+          <t>1204006</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1225748</t>
+          <t>1307051</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2166357</t>
+          <t>2398212</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1867144</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2325161</t>
+          <t>2478695</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1813946</t>
+          <t>1969227</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1350780</t>
+          <t>1897038</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1979854</t>
+          <t>2033875</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2084130</t>
+          <t>1970455</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1959813</t>
+          <t>1913517</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2344653</t>
+          <t>2019294</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3898076</t>
+          <t>3939682</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3482742</t>
+          <t>3850363</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4132562</t>
+          <t>4021284</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
